--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_araucania.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.43279118184796</v>
+      </c>
+      <c r="C2">
         <v>26.75882185092419</v>
-      </c>
-      <c r="C2">
-        <v>26.43279118184796</v>
       </c>
       <c r="D2">
         <v>3.737085308056872</v>
       </c>
       <c r="E2">
-        <v>17.46755016229231</v>
+        <v>17.25472475845869</v>
       </c>
       <c r="F2">
         <v>65.27772507924901</v>
       </c>
       <c r="G2">
-        <v>17.25472475845869</v>
+        <v>17.46755016229231</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>32.46985876679297</v>
+      </c>
+      <c r="C3">
         <v>36.67929727867723</v>
-      </c>
-      <c r="C3">
-        <v>32.46985876679297</v>
       </c>
       <c r="D3">
         <v>2.7263335837716</v>
       </c>
       <c r="E3">
-        <v>21.68458781362007</v>
+        <v>19.19599217986315</v>
       </c>
       <c r="F3">
         <v>59.11942000651678</v>
       </c>
       <c r="G3">
-        <v>19.19599217986315</v>
+        <v>21.68458781362007</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.19704064431541</v>
+      </c>
+      <c r="C4">
         <v>42.14272335643378</v>
-      </c>
-      <c r="C4">
-        <v>32.19704064431541</v>
       </c>
       <c r="D4">
         <v>2.372888888888889</v>
       </c>
       <c r="E4">
-        <v>24.17275461968199</v>
+        <v>18.46798452943704</v>
       </c>
       <c r="F4">
         <v>57.35926085088096</v>
       </c>
       <c r="G4">
-        <v>18.46798452943704</v>
+        <v>24.17275461968199</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.80066445182724</v>
+      </c>
+      <c r="C5">
         <v>29.85880398671096</v>
-      </c>
-      <c r="C5">
-        <v>34.80066445182724</v>
       </c>
       <c r="D5">
         <v>3.349095966620306</v>
       </c>
       <c r="E5">
-        <v>18.13366960907945</v>
+        <v>21.13493064312736</v>
       </c>
       <c r="F5">
         <v>60.73139974779319</v>
       </c>
       <c r="G5">
-        <v>21.13493064312736</v>
+        <v>18.13366960907945</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.24516750361147</v>
+      </c>
+      <c r="C6">
         <v>34.76645800371465</v>
-      </c>
-      <c r="C6">
-        <v>28.24516750361147</v>
       </c>
       <c r="D6">
         <v>2.876335575781559</v>
       </c>
       <c r="E6">
-        <v>21.32759421023758</v>
+        <v>17.32708781702325</v>
       </c>
       <c r="F6">
         <v>61.34531797273917</v>
       </c>
       <c r="G6">
-        <v>17.32708781702325</v>
+        <v>21.32759421023758</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>34.72241842068089</v>
+      </c>
+      <c r="C7">
         <v>34.01610396948722</v>
-      </c>
-      <c r="C7">
-        <v>34.72241842068089</v>
       </c>
       <c r="D7">
         <v>2.939784053156146</v>
       </c>
       <c r="E7">
+        <v>20.57764755127669</v>
+      </c>
+      <c r="F7">
+        <v>59.26329007953119</v>
+      </c>
+      <c r="G7">
         <v>20.15906236919213</v>
-      </c>
-      <c r="F7">
-        <v>59.26329007953117</v>
-      </c>
-      <c r="G7">
-        <v>20.57764755127668</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.0836391947503</v>
+      </c>
+      <c r="C8">
         <v>39.67300633967301</v>
-      </c>
-      <c r="C8">
-        <v>28.0836391947503</v>
       </c>
       <c r="D8">
         <v>2.520605550883095</v>
       </c>
       <c r="E8">
-        <v>23.64914141748989</v>
+        <v>16.74070145196579</v>
       </c>
       <c r="F8">
         <v>59.61015713054432</v>
       </c>
       <c r="G8">
-        <v>16.74070145196579</v>
+        <v>23.64914141748989</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.29186602870813</v>
+      </c>
+      <c r="C9">
         <v>28.32934609250399</v>
-      </c>
-      <c r="C9">
-        <v>31.29186602870813</v>
       </c>
       <c r="D9">
         <v>3.52990851513019</v>
       </c>
       <c r="E9">
-        <v>17.74785801713586</v>
+        <v>19.60382684285464</v>
       </c>
       <c r="F9">
         <v>62.64831514000949</v>
       </c>
       <c r="G9">
-        <v>19.60382684285464</v>
+        <v>17.74785801713586</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.34812953657175</v>
+      </c>
+      <c r="C10">
         <v>35.29452819653824</v>
-      </c>
-      <c r="C10">
-        <v>29.34812953657175</v>
       </c>
       <c r="D10">
         <v>2.833300375716828</v>
       </c>
       <c r="E10">
-        <v>21.43704959728699</v>
+        <v>17.82534972445952</v>
       </c>
       <c r="F10">
         <v>60.7376006782535</v>
       </c>
       <c r="G10">
-        <v>17.82534972445952</v>
+        <v>21.43704959728699</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>32.46719160104987</v>
+      </c>
+      <c r="C11">
         <v>39.60629921259842</v>
-      </c>
-      <c r="C11">
-        <v>32.46719160104987</v>
       </c>
       <c r="D11">
         <v>2.524850894632207</v>
       </c>
       <c r="E11">
-        <v>23.01708358755338</v>
+        <v>18.86821232458816</v>
       </c>
       <c r="F11">
         <v>58.11470408785845</v>
       </c>
       <c r="G11">
-        <v>18.86821232458816</v>
+        <v>23.01708358755338</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.82257269590932</v>
+      </c>
+      <c r="C12">
         <v>33.97732873336619</v>
-      </c>
-      <c r="C12">
-        <v>29.82257269590932</v>
       </c>
       <c r="D12">
         <v>2.943138961415724</v>
       </c>
       <c r="E12">
-        <v>20.74319241763202</v>
+        <v>18.20670979389198</v>
       </c>
       <c r="F12">
         <v>61.050097788476</v>
       </c>
       <c r="G12">
-        <v>18.20670979389198</v>
+        <v>20.74319241763202</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>31.42105816766593</v>
+      </c>
+      <c r="C13">
         <v>24.99631850215631</v>
-      </c>
-      <c r="C13">
-        <v>31.42105816766593</v>
       </c>
       <c r="D13">
         <v>4.000589126409696</v>
       </c>
       <c r="E13">
-        <v>15.98052533186287</v>
+        <v>20.08795879117184</v>
       </c>
       <c r="F13">
         <v>63.93151587696529</v>
       </c>
       <c r="G13">
-        <v>20.08795879117184</v>
+        <v>15.98052533186287</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>32.69362577107608</v>
+      </c>
+      <c r="C14">
         <v>32.12245830477496</v>
-      </c>
-      <c r="C14">
-        <v>32.69362577107608</v>
       </c>
       <c r="D14">
         <v>3.113086770981508</v>
       </c>
       <c r="E14">
-        <v>19.48988078735791</v>
+        <v>19.8364291655115</v>
       </c>
       <c r="F14">
         <v>60.67369004713058</v>
       </c>
       <c r="G14">
-        <v>19.8364291655115</v>
+        <v>19.48988078735791</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.5222278998467</v>
+      </c>
+      <c r="C15">
         <v>34.41492079713848</v>
-      </c>
-      <c r="C15">
-        <v>29.5222278998467</v>
       </c>
       <c r="D15">
         <v>2.905716406829993</v>
       </c>
       <c r="E15">
-        <v>20.992753058521</v>
+        <v>18.00825995480402</v>
       </c>
       <c r="F15">
         <v>60.99898698667498</v>
       </c>
       <c r="G15">
-        <v>18.00825995480402</v>
+        <v>20.992753058521</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>30.72465179701958</v>
+      </c>
+      <c r="C16">
         <v>24.05279049381513</v>
-      </c>
-      <c r="C16">
-        <v>30.72465179701958</v>
       </c>
       <c r="D16">
         <v>4.157521765539583</v>
       </c>
       <c r="E16">
+        <v>19.8508589767793</v>
+      </c>
+      <c r="F16">
+        <v>64.60889811843181</v>
+      </c>
+      <c r="G16">
         <v>15.54024290478887</v>
-      </c>
-      <c r="F16">
-        <v>64.60889811843182</v>
-      </c>
-      <c r="G16">
-        <v>19.85085897677931</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>35.36673928830791</v>
+      </c>
+      <c r="C17">
         <v>39.23021060275963</v>
-      </c>
-      <c r="C17">
-        <v>35.36673928830791</v>
       </c>
       <c r="D17">
         <v>2.549055905220289</v>
       </c>
       <c r="E17">
-        <v>22.46901256135097</v>
+        <v>20.2562182846685</v>
       </c>
       <c r="F17">
         <v>57.27476915398054</v>
       </c>
       <c r="G17">
-        <v>20.2562182846685</v>
+        <v>22.46901256135097</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>32.00235571260306</v>
+      </c>
+      <c r="C18">
         <v>39.37573616018846</v>
-      </c>
-      <c r="C18">
-        <v>32.00235571260306</v>
       </c>
       <c r="D18">
         <v>2.539635058330841</v>
       </c>
       <c r="E18">
-        <v>22.97594501718213</v>
+        <v>18.67353951890034</v>
       </c>
       <c r="F18">
         <v>58.35051546391752</v>
       </c>
       <c r="G18">
-        <v>18.67353951890034</v>
+        <v>22.97594501718213</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>29.40768964322826</v>
+      </c>
+      <c r="C19">
         <v>37.54762729476966</v>
-      </c>
-      <c r="C19">
-        <v>29.40768964322826</v>
       </c>
       <c r="D19">
         <v>2.663284132841329</v>
       </c>
       <c r="E19">
-        <v>22.4896265560166</v>
+        <v>17.61410788381743</v>
       </c>
       <c r="F19">
         <v>59.89626556016598</v>
       </c>
       <c r="G19">
-        <v>17.61410788381743</v>
+        <v>22.4896265560166</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>31.56621081659069</v>
+      </c>
+      <c r="C20">
         <v>28.08824357026282</v>
-      </c>
-      <c r="C20">
-        <v>31.56621081659069</v>
       </c>
       <c r="D20">
         <v>3.560208375075135</v>
       </c>
       <c r="E20">
-        <v>17.59314744968099</v>
+        <v>19.771581656033</v>
       </c>
       <c r="F20">
         <v>62.63527089428602</v>
       </c>
       <c r="G20">
-        <v>19.771581656033</v>
+        <v>17.59314744968099</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>31.62606288806324</v>
+      </c>
+      <c r="C21">
         <v>28.9454654265267</v>
-      </c>
-      <c r="C21">
-        <v>31.62606288806324</v>
       </c>
       <c r="D21">
         <v>3.454772570640937</v>
       </c>
       <c r="E21">
-        <v>18.02652421033015</v>
+        <v>19.69593440382644</v>
       </c>
       <c r="F21">
         <v>62.27754138584339</v>
       </c>
       <c r="G21">
-        <v>19.69593440382644</v>
+        <v>18.02652421033015</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>37.25170471390454</v>
+      </c>
+      <c r="C22">
         <v>32.38956418618441</v>
-      </c>
-      <c r="C22">
-        <v>37.25170471390454</v>
       </c>
       <c r="D22">
         <v>3.087414187643021</v>
       </c>
       <c r="E22">
-        <v>19.092974484446</v>
+        <v>21.95910520796924</v>
       </c>
       <c r="F22">
         <v>58.94792030758477</v>
       </c>
       <c r="G22">
-        <v>21.95910520796924</v>
+        <v>19.092974484446</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>29.39301630281492</v>
+      </c>
+      <c r="C23">
         <v>31.33637953404411</v>
-      </c>
-      <c r="C23">
-        <v>29.39301630281492</v>
       </c>
       <c r="D23">
         <v>3.191179117911791</v>
       </c>
       <c r="E23">
-        <v>19.49635869088356</v>
+        <v>18.28726857945074</v>
       </c>
       <c r="F23">
         <v>62.2163727296657</v>
       </c>
       <c r="G23">
-        <v>18.28726857945074</v>
+        <v>19.49635869088356</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>31.05375533785481</v>
+      </c>
+      <c r="C24">
         <v>30.44461190655614</v>
-      </c>
-      <c r="C24">
-        <v>31.05375533785481</v>
       </c>
       <c r="D24">
         <v>3.284653465346535</v>
       </c>
       <c r="E24">
-        <v>18.85134346930047</v>
+        <v>19.22852587782401</v>
       </c>
       <c r="F24">
         <v>61.92013065287554</v>
       </c>
       <c r="G24">
-        <v>19.22852587782401</v>
+        <v>18.85134346930047</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>29.70004614674665</v>
+      </c>
+      <c r="C25">
         <v>40.62759575449931</v>
-      </c>
-      <c r="C25">
-        <v>29.70004614674665</v>
       </c>
       <c r="D25">
         <v>2.461381190368015</v>
       </c>
       <c r="E25">
-        <v>23.85261446762395</v>
+        <v>17.43700894066649</v>
       </c>
       <c r="F25">
         <v>58.71037659170957</v>
       </c>
       <c r="G25">
-        <v>17.43700894066649</v>
+        <v>23.85261446762395</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>38.34435758669072</v>
+      </c>
+      <c r="C26">
         <v>31.36901182601724</v>
-      </c>
-      <c r="C26">
-        <v>38.34435758669072</v>
       </c>
       <c r="D26">
         <v>3.187859424920128</v>
       </c>
       <c r="E26">
-        <v>18.48352427069801</v>
+        <v>22.59359867721744</v>
       </c>
       <c r="F26">
         <v>58.92287705208457</v>
       </c>
       <c r="G26">
-        <v>22.59359867721744</v>
+        <v>18.48352427069801</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>34.34994497720484</v>
+      </c>
+      <c r="C27">
         <v>30.90709008017608</v>
-      </c>
-      <c r="C27">
-        <v>34.34994497720484</v>
       </c>
       <c r="D27">
         <v>3.235503560528993</v>
       </c>
       <c r="E27">
-        <v>18.70243531202435</v>
+        <v>20.78576864535769</v>
       </c>
       <c r="F27">
-        <v>60.51179604261795</v>
+        <v>60.51179604261797</v>
       </c>
       <c r="G27">
-        <v>20.78576864535768</v>
+        <v>18.70243531202436</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.72280456557186</v>
+      </c>
+      <c r="C28">
         <v>36.96715583508036</v>
-      </c>
-      <c r="C28">
-        <v>29.72280456557186</v>
       </c>
       <c r="D28">
         <v>2.705103969754253</v>
       </c>
       <c r="E28">
+        <v>17.83119060927892</v>
+      </c>
+      <c r="F28">
+        <v>59.99161542761318</v>
+      </c>
+      <c r="G28">
         <v>22.17719396310788</v>
-      </c>
-      <c r="F28">
-        <v>59.9916154276132</v>
-      </c>
-      <c r="G28">
-        <v>17.83119060927893</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.29115341545353</v>
+      </c>
+      <c r="C29">
         <v>34.95707353490108</v>
-      </c>
-      <c r="C29">
-        <v>30.29115341545353</v>
       </c>
       <c r="D29">
         <v>2.860651361452216</v>
       </c>
       <c r="E29">
-        <v>21.15428055116331</v>
+        <v>18.33069798960922</v>
       </c>
       <c r="F29">
-        <v>60.51502145922746</v>
+        <v>60.51502145922748</v>
       </c>
       <c r="G29">
-        <v>18.33069798960922</v>
+        <v>21.15428055116332</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>31.39332171114389</v>
+      </c>
+      <c r="C30">
         <v>35.38956684993965</v>
-      </c>
-      <c r="C30">
-        <v>31.39332171114389</v>
       </c>
       <c r="D30">
         <v>2.825691549829481</v>
       </c>
       <c r="E30">
-        <v>21.21894347511458</v>
+        <v>18.82286725094476</v>
       </c>
       <c r="F30">
         <v>59.95818927394066</v>
       </c>
       <c r="G30">
-        <v>18.82286725094476</v>
+        <v>21.21894347511458</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>31.77267826890498</v>
+      </c>
+      <c r="C31">
         <v>31.32604343138765</v>
-      </c>
-      <c r="C31">
-        <v>31.77267826890498</v>
       </c>
       <c r="D31">
         <v>3.192232055063914</v>
       </c>
       <c r="E31">
-        <v>19.20679886685553</v>
+        <v>19.48064211520302</v>
       </c>
       <c r="F31">
-        <v>61.31255901794146</v>
+        <v>61.31255901794145</v>
       </c>
       <c r="G31">
-        <v>19.48064211520303</v>
+        <v>19.20679886685552</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>31.33620689655172</v>
+      </c>
+      <c r="C32">
         <v>38.77586206896552</v>
-      </c>
-      <c r="C32">
-        <v>31.33620689655172</v>
       </c>
       <c r="D32">
         <v>2.578923966207203</v>
       </c>
       <c r="E32">
-        <v>22.79430395783713</v>
+        <v>18.420919272285</v>
       </c>
       <c r="F32">
         <v>58.78477676987787</v>
       </c>
       <c r="G32">
-        <v>18.420919272285</v>
+        <v>22.79430395783713</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>27.82966006723945</v>
+      </c>
+      <c r="C33">
         <v>34.5816212177811</v>
-      </c>
-      <c r="C33">
-        <v>27.82966006723945</v>
       </c>
       <c r="D33">
         <v>2.89170942479071</v>
       </c>
       <c r="E33">
-        <v>21.29262262089587</v>
+        <v>17.13529986774768</v>
       </c>
       <c r="F33">
         <v>61.57207751135645</v>
       </c>
       <c r="G33">
-        <v>17.13529986774768</v>
+        <v>21.29262262089587</v>
       </c>
     </row>
   </sheetData>
